--- a/data/Mörel-Filet/investment_decision/Breiten_MFH_from_2015_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Breiten_MFH_from_2015_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>12.51210950258506</v>
+        <v>6.969697177594109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>1737.840424201838</v>
       </c>
       <c r="F2" t="n">
-        <v>12.49648877780668</v>
+        <v>6.682221047110841</v>
       </c>
       <c r="G2" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="H2" t="n">
-        <v>12.51210950258506</v>
+        <v>6.617889339529407</v>
       </c>
       <c r="I2" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="J2" t="n">
-        <v>12.51210950258506</v>
+        <v>7.074340504200737</v>
       </c>
       <c r="K2" t="n">
         <v>1737.840424201838</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>12.51210950258506</v>
+        <v>6.969697177594109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>1737.840424201838</v>
       </c>
       <c r="F3" t="n">
-        <v>12.49648877780668</v>
+        <v>6.682221047110841</v>
       </c>
       <c r="G3" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="H3" t="n">
-        <v>12.51210950258506</v>
+        <v>6.617889339529407</v>
       </c>
       <c r="I3" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="J3" t="n">
-        <v>12.51210950258506</v>
+        <v>7.074340504200737</v>
       </c>
       <c r="K3" t="n">
         <v>1737.840424201838</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>12.51210950258506</v>
+        <v>6.969697177594109</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>1737.840424201838</v>
       </c>
       <c r="F4" t="n">
-        <v>12.49648877780668</v>
+        <v>6.682221047110841</v>
       </c>
       <c r="G4" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="H4" t="n">
-        <v>12.51210950258506</v>
+        <v>6.617889339529407</v>
       </c>
       <c r="I4" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="J4" t="n">
-        <v>12.51210950258506</v>
+        <v>7.074340504200737</v>
       </c>
       <c r="K4" t="n">
         <v>1737.840424201838</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>12.68915706265703</v>
+        <v>6.969697177594109</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>1737.840424201838</v>
       </c>
       <c r="F5" t="n">
-        <v>12.68915706265703</v>
+        <v>6.682221047110841</v>
       </c>
       <c r="G5" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="H5" t="n">
-        <v>12.68915706265703</v>
+        <v>6.617889339529407</v>
       </c>
       <c r="I5" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="J5" t="n">
-        <v>12.68915706265703</v>
+        <v>7.074340504200737</v>
       </c>
       <c r="K5" t="n">
         <v>1737.840424201838</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>12.82108363884983</v>
+        <v>6.969697177594109</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>1737.840424201838</v>
       </c>
       <c r="F6" t="n">
-        <v>12.82108363884983</v>
+        <v>6.682221047110841</v>
       </c>
       <c r="G6" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="H6" t="n">
-        <v>12.82108363884983</v>
+        <v>6.617889339529407</v>
       </c>
       <c r="I6" t="n">
         <v>1737.840424201838</v>
       </c>
       <c r="J6" t="n">
-        <v>12.82108363884983</v>
+        <v>7.074340504200737</v>
       </c>
       <c r="K6" t="n">
         <v>1737.840424201838</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Breiten_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Breiten_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.606760636302757</v>
+        <v>5.236110000000001</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001101319715294119</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001101319715294118</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001117701844533935</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001117701844533935</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001117701844533935</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001117701844533935</v>
+        <v>0.0009576693176470589</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02460223536296389</v>
+        <v>0.03343352384466152</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02460223536296389</v>
+        <v>0.03438128984673951</v>
       </c>
       <c r="G17" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02460223536296389</v>
+        <v>0.03463710036419116</v>
       </c>
       <c r="I17" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02460223536296389</v>
+        <v>0.03308853037638511</v>
       </c>
       <c r="K17" t="n">
         <v>0.1709439732</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.0758272736123559</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.07525318711138199</v>
       </c>
       <c r="G18" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.07301111285849032</v>
       </c>
       <c r="I18" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.0748603952716773</v>
       </c>
       <c r="K18" t="n">
         <v>0.1709439732</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.07582727361235592</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.07525318711138199</v>
       </c>
       <c r="G19" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.07301111285849041</v>
       </c>
       <c r="I19" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1179199650946944</v>
+        <v>0.0748603952716773</v>
       </c>
       <c r="K19" t="n">
         <v>0.1709439732</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1119276015</v>
+        <v>0.05596380074999999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1119276015</v>
+        <v>0.05596380074999999</v>
       </c>
       <c r="G20" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1119276015</v>
+        <v>0.05502072664874221</v>
       </c>
       <c r="I20" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1119276015</v>
+        <v>0.05596380074999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.1709439732</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01860987176826946</v>
+        <v>0.0135700509823056</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01860987176826946</v>
+        <v>0.01509190348535751</v>
       </c>
       <c r="G21" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01860987176826946</v>
+        <v>0.01664671415444295</v>
       </c>
       <c r="I21" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J21" t="n">
-        <v>0.01860987176826946</v>
+        <v>0.01419193585470779</v>
       </c>
       <c r="K21" t="n">
         <v>0.1709439732</v>
@@ -1420,7 +1420,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0305257095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.0305257095</v>
       </c>
       <c r="G27" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.03048199104458776</v>
       </c>
       <c r="I27" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.0305257095</v>
       </c>
       <c r="K27" t="n">
         <v>0.1709439732</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.04498652769528933</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.04556061419626325</v>
       </c>
       <c r="G28" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.04780268844915491</v>
       </c>
       <c r="I28" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.04595340603596793</v>
       </c>
       <c r="K28" t="n">
         <v>0.1709439732</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.04807651105401808</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.04872832530762549</v>
       </c>
       <c r="G29" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.0508761825</v>
       </c>
       <c r="I29" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.05023549620223505</v>
       </c>
       <c r="K29" t="n">
         <v>0.1709439732</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.05596380075000001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.05596380075000001</v>
       </c>
       <c r="G30" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.05690687485125778</v>
       </c>
       <c r="I30" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.05596380075000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.1709439732</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.0508761825</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.1709439732</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.05128400453726212</v>
       </c>
       <c r="G31" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.05165108208241557</v>
       </c>
       <c r="I31" t="n">
         <v>0.1709439732</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.05133172175808596</v>
       </c>
       <c r="K31" t="n">
         <v>0.1709439732</v>
@@ -2160,7 +2160,7 @@
         <v>46023</v>
       </c>
       <c r="B47" t="n">
-        <v>0.08054891268946038</v>
+        <v>0.06347343260013966</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2174,19 +2174,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F47" t="n">
-        <v>0.08304328710748236</v>
+        <v>0.06869791618655405</v>
       </c>
       <c r="G47" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H47" t="n">
-        <v>0.08304328710748235</v>
+        <v>0.06912812818628683</v>
       </c>
       <c r="I47" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J47" t="n">
-        <v>0.08054891268946039</v>
+        <v>0.06485066886505214</v>
       </c>
       <c r="K47" t="n">
         <v>0.6143422994209518</v>
@@ -2197,7 +2197,7 @@
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.08054891268946038</v>
+        <v>0.06347343260013966</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2211,19 +2211,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F48" t="n">
-        <v>0.08304328710748236</v>
+        <v>0.06869791618655405</v>
       </c>
       <c r="G48" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H48" t="n">
-        <v>0.08304328710748235</v>
+        <v>0.06912812818628683</v>
       </c>
       <c r="I48" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J48" t="n">
-        <v>0.08054891268946039</v>
+        <v>0.06485066886505214</v>
       </c>
       <c r="K48" t="n">
         <v>0.6143422994209518</v>
@@ -2234,7 +2234,7 @@
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.08054891268946038</v>
+        <v>0.06347343260013966</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2248,19 +2248,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F49" t="n">
-        <v>0.08304328710748236</v>
+        <v>0.06869791618655405</v>
       </c>
       <c r="G49" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08304328710748235</v>
+        <v>0.06912812818628683</v>
       </c>
       <c r="I49" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J49" t="n">
-        <v>0.08054891268946039</v>
+        <v>0.06485066886505214</v>
       </c>
       <c r="K49" t="n">
         <v>0.6143422994209518</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1367730179478111</v>
+        <v>0.1422803015258363</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1174444616246357</v>
+        <v>0.1251729885668998</v>
       </c>
       <c r="G52" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1172542250686139</v>
+        <v>0.1238997898038777</v>
       </c>
       <c r="I52" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J52" t="n">
-        <v>0.1367730179478111</v>
+        <v>0.140943149167382</v>
       </c>
       <c r="K52" t="n">
         <v>0.6143422994209518</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1367730179478111</v>
+        <v>0.1422803015258363</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1174444616246357</v>
+        <v>0.1251729885668998</v>
       </c>
       <c r="G53" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1172542250686139</v>
+        <v>0.1238997898038777</v>
       </c>
       <c r="I53" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J53" t="n">
-        <v>0.1367730179478111</v>
+        <v>0.140943149167382</v>
       </c>
       <c r="K53" t="n">
         <v>0.6143422994209518</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1367730179478111</v>
+        <v>0.1422803015258363</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1174444616246357</v>
+        <v>0.1251729885668998</v>
       </c>
       <c r="G54" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1172542250686139</v>
+        <v>0.1238997898038777</v>
       </c>
       <c r="I54" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1367730179478111</v>
+        <v>0.140943149167382</v>
       </c>
       <c r="K54" t="n">
         <v>0.6143422994209518</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1566908270058224</v>
+        <v>0.1571234909478111</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1532867488572175</v>
+        <v>0.1558275215314797</v>
       </c>
       <c r="G55" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1532867488572175</v>
+        <v>0.1558241393577066</v>
       </c>
       <c r="I55" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1565648497532632</v>
+        <v>0.1573512605768541</v>
       </c>
       <c r="K55" t="n">
         <v>0.6143422994209518</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.157588942153986</v>
+        <v>0.1571234909478111</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1532867488572175</v>
+        <v>0.1558275215314797</v>
       </c>
       <c r="G56" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1532867488572175</v>
+        <v>0.1558241393577066</v>
       </c>
       <c r="I56" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J56" t="n">
-        <v>0.157588942153986</v>
+        <v>0.1573512605768541</v>
       </c>
       <c r="K56" t="n">
         <v>0.6143422994209518</v>
@@ -2715,7 +2715,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.03994040072881627</v>
+        <v>0.01367461021866338</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,19 +2729,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04495688412919727</v>
+        <v>0.01582207757777005</v>
       </c>
       <c r="G62" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H62" t="n">
-        <v>0.04495688412919729</v>
+        <v>0.01622869480475707</v>
       </c>
       <c r="I62" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03994040072881629</v>
+        <v>0.01207107714694553</v>
       </c>
       <c r="K62" t="n">
         <v>0.6143422994209518</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.03994040072881627</v>
+        <v>0.01367461021866338</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04495688412919727</v>
+        <v>0.01582207757777005</v>
       </c>
       <c r="G63" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H63" t="n">
-        <v>0.04495688412919729</v>
+        <v>0.01622869480475707</v>
       </c>
       <c r="I63" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J63" t="n">
-        <v>0.03994040072881629</v>
+        <v>0.01207107714694553</v>
       </c>
       <c r="K63" t="n">
         <v>0.6143422994209518</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.03994040072881627</v>
+        <v>0.01367461021866338</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04495688412919727</v>
+        <v>0.01582207757777005</v>
       </c>
       <c r="G64" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H64" t="n">
-        <v>0.04495688412919729</v>
+        <v>0.01622869480475707</v>
       </c>
       <c r="I64" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03994040072881629</v>
+        <v>0.01207107714694553</v>
       </c>
       <c r="K64" t="n">
         <v>0.6143422994209518</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.05318958092611271</v>
+        <v>0.02982712895420554</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0565936590747177</v>
+        <v>0.03165733001705279</v>
       </c>
       <c r="G65" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0565936590747177</v>
+        <v>0.03178026310451965</v>
       </c>
       <c r="I65" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J65" t="n">
-        <v>0.05331555817867196</v>
+        <v>0.02940489526104711</v>
       </c>
       <c r="K65" t="n">
         <v>0.6143422994209518</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.08269874522339633</v>
+        <v>0.05953826626928687</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F66" t="n">
-        <v>0.08700093852016484</v>
+        <v>0.06141831009501904</v>
       </c>
       <c r="G66" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H66" t="n">
-        <v>0.08700093852016484</v>
+        <v>0.06172771082138823</v>
       </c>
       <c r="I66" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J66" t="n">
-        <v>0.08269874522339633</v>
+        <v>0.05924175224761443</v>
       </c>
       <c r="K66" t="n">
         <v>0.6143422994209518</v>
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.03451817465423294</v>
+        <v>0.03416134979120394</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,19 +3284,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F77" t="n">
-        <v>0.04640909530640393</v>
+        <v>0.04596410941244205</v>
       </c>
       <c r="G77" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H77" t="n">
-        <v>0.04652610971502718</v>
+        <v>0.04686312333642773</v>
       </c>
       <c r="I77" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J77" t="n">
-        <v>0.03451817465423289</v>
+        <v>0.03497225173545614</v>
       </c>
       <c r="K77" t="n">
         <v>0.6143422994209518</v>
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.03451817465423294</v>
+        <v>0.03416134979120394</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,19 +3321,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F78" t="n">
-        <v>0.04640909530640393</v>
+        <v>0.04596410941244205</v>
       </c>
       <c r="G78" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H78" t="n">
-        <v>0.04652610971502718</v>
+        <v>0.04686312333642773</v>
       </c>
       <c r="I78" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J78" t="n">
-        <v>0.03451817465423289</v>
+        <v>0.03497225173545614</v>
       </c>
       <c r="K78" t="n">
         <v>0.6143422994209518</v>
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.03451817465423294</v>
+        <v>0.03416134979120394</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,19 +3358,19 @@
         <v>0.6143422994209518</v>
       </c>
       <c r="F79" t="n">
-        <v>0.04640909530640393</v>
+        <v>0.04596410941244205</v>
       </c>
       <c r="G79" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="H79" t="n">
-        <v>0.04652610971502718</v>
+        <v>0.04686312333642773</v>
       </c>
       <c r="I79" t="n">
         <v>0.6143422994209518</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0345181746542329</v>
+        <v>0.03497225173545614</v>
       </c>
       <c r="K79" t="n">
         <v>0.6143422994209518</v>
